--- a/Tests/Validation/Barley/Observations/RS14_15_Biomass.xlsx
+++ b/Tests/Validation/Barley/Observations/RS14_15_Biomass.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubRepos\ApsimX\Prototypes\Barley\Observations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Repos\ApsimX\Tests\Validation\Barley\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB10DB03-7FF8-4E42-9468-C27134E34366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9105"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,12 +51,6 @@
     <t>Barley.Leaf.LAI</t>
   </si>
   <si>
-    <t>Barley.Structure.MainStemPop</t>
-  </si>
-  <si>
-    <t>Barley.Leaf.SLA</t>
-  </si>
-  <si>
     <t>Barley.Grain.Size</t>
   </si>
   <si>
@@ -90,12 +85,18 @@
   </si>
   <si>
     <t>RS2014_15CultOmakaIrrMed</t>
+  </si>
+  <si>
+    <t>Barley.Leaf.MainStemPopulation</t>
+  </si>
+  <si>
+    <t>Barley.Leaf.SpecificLeafCanopy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -154,7 +155,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,15 +436,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,27 +470,27 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
       </c>
       <c r="B2" s="3">
         <v>41968</v>
@@ -504,10 +505,10 @@
         <v>58.721774354503133</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>2.73936692715754</v>
@@ -519,9 +520,9 @@
         <v>15381.241388337288</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3">
         <v>41982</v>
@@ -536,10 +537,10 @@
         <v>368.35038592888702</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>5.0595878451672665</v>
@@ -551,9 +552,9 @@
         <v>8618.167204035437</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3">
         <v>41995</v>
@@ -583,9 +584,9 @@
         <v>5759.409148525976</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3">
         <v>42019</v>
@@ -615,9 +616,9 @@
         <v>1976.5189080765419</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3">
         <v>41968</v>
@@ -632,10 +633,10 @@
         <v>37.57573201119154</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>1.5001330304815867</v>
@@ -647,9 +648,9 @@
         <v>13627.2192879717</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3">
         <v>41982</v>
@@ -667,7 +668,7 @@
         <v>9.4486720653872064E-2</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>1.9834841250229505</v>
@@ -679,9 +680,9 @@
         <v>6487.1481610306182</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3">
         <v>41995</v>
@@ -711,9 +712,9 @@
         <v>3577.1309884330599</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3">
         <v>42019</v>
@@ -743,9 +744,9 @@
         <v>304.45483540288694</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3">
         <v>41968</v>
@@ -760,10 +761,10 @@
         <v>36.428112367700656</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>1.5501057765391122</v>
@@ -775,9 +776,9 @@
         <v>13698.098196122137</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3">
         <v>41982</v>
@@ -792,10 +793,10 @@
         <v>184.04856465768916</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>1.8047943002087652</v>
@@ -807,9 +808,9 @@
         <v>6356.9497258809906</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3">
         <v>41995</v>
@@ -839,9 +840,9 @@
         <v>3735.8656059691175</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3">
         <v>42019</v>
@@ -871,9 +872,9 @@
         <v>1089.4177481965999</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3">
         <v>41968</v>
@@ -888,10 +889,10 @@
         <v>62.742241042003037</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>2.6162008823206291</v>
@@ -903,9 +904,9 @@
         <v>14165.758755236169</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3">
         <v>41982</v>
@@ -923,7 +924,7 @@
         <v>7.9313526077790242E-2</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>4.1098381508868993</v>
@@ -935,9 +936,9 @@
         <v>7419.1654440321945</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
         <v>41995</v>
@@ -967,9 +968,9 @@
         <v>5487.9968483039775</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>42019</v>
@@ -999,9 +1000,9 @@
         <v>1579.1174953319096</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>41968</v>
@@ -1016,10 +1017,10 @@
         <v>42.222189659324727</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18">
         <v>1.8410014694007311</v>
@@ -1031,9 +1032,9 @@
         <v>13171.745786288448</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="3">
         <v>41982</v>
@@ -1048,10 +1049,10 @@
         <v>231.00840037161362</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H19">
         <v>2.4976912949280297</v>
@@ -1063,9 +1064,9 @@
         <v>6486.1670921127516</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3">
         <v>41995</v>
@@ -1095,9 +1096,9 @@
         <v>3580.2610551738608</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" s="3">
         <v>42019</v>
@@ -1127,9 +1128,9 @@
         <v>230.11503871296151</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3">
         <v>41968</v>
@@ -1144,10 +1145,10 @@
         <v>39.743241105720088</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>1.5256542222354492</v>
@@ -1159,9 +1160,9 @@
         <v>12000.64465509909</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="3">
         <v>41982</v>
@@ -1176,10 +1177,10 @@
         <v>220.41187200486402</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>2.2446708010119716</v>
@@ -1191,9 +1192,9 @@
         <v>6154.8530858570084</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="3">
         <v>41995</v>
@@ -1208,7 +1209,7 @@
         <v>389.53984164332462</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>176.38262354620196</v>
@@ -1223,9 +1224,9 @@
         <v>3818.1690939989203</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
         <v>42019</v>
@@ -1255,9 +1256,9 @@
         <v>824.74499209828264</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B26" s="3">
         <v>42046</v>
@@ -1287,12 +1288,12 @@
         <v>1042.6683655494774</v>
       </c>
       <c r="N26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>16</v>
       </c>
       <c r="B27" s="3">
         <v>42032</v>
@@ -1322,12 +1323,12 @@
         <v>596.24842055924114</v>
       </c>
       <c r="N27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" s="3">
         <v>42046</v>
@@ -1357,12 +1358,12 @@
         <v>788.99579370255992</v>
       </c>
       <c r="N28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B29" s="3">
         <v>42046</v>
@@ -1392,12 +1393,12 @@
         <v>803.27547646829487</v>
       </c>
       <c r="N29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B30" s="3">
         <v>42032</v>
@@ -1427,12 +1428,12 @@
         <v>560.59100038429619</v>
       </c>
       <c r="N30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B31" s="3">
         <v>42046</v>
@@ -1462,7 +1463,7 @@
         <v>699.351811485182</v>
       </c>
       <c r="N31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
